--- a/conte/第1回_コンテ表_v2.xlsx
+++ b/conte/第1回_コンテ表_v2.xlsx
@@ -4799,15 +4799,19 @@
           <t>バーネイズは、精神分析の医者に相談しました。返ってきた助言は、こうだったといいます。——たばこは、力の象徴だ。女性にとっては、自分の「たいまつ」になる。</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>助言は少し声を落として、内緒話の温度で</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>診察室のシルエット(AI生成・抽象寄り。人物特定できない画)</t>
+          <t>切り絵コラージュ(collage): Gemini静止画の医者/診察室を切り抜き、古紙・診療録テクスチャ板の上に配置。Ken Burnsで緩速。実在人物に似せない架空。生成AI動画は使わない(v4.4)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>生成AI(Runway/Gemini)</t>
+          <t>Remotion(モンタージュ)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4867,7 +4871,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MNT_COLLAGE_DOCTOR</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
